--- a/generated_reports/monthly_attendance_report_march_2026_maintenance.xlsx
+++ b/generated_reports/monthly_attendance_report_march_2026_maintenance.xlsx
@@ -168,7 +168,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -239,6 +239,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -464,7 +470,7 @@
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
@@ -683,6 +689,14 @@
     </xf>
     <xf numFmtId="1" fontId="19" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="6">
@@ -2870,9 +2884,9 @@
       <c r="A13" s="62" t="n">
         <v>46088</v>
       </c>
-      <c r="B13" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B13" s="76" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C13" s="68" t="n">
@@ -3108,9 +3122,9 @@
       <c r="A20" s="62" t="n">
         <v>46095</v>
       </c>
-      <c r="B20" s="71" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B20" s="76" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C20" s="72" t="n">
@@ -3227,7 +3241,7 @@
       </c>
       <c r="H23" s="69" t="inlineStr">
         <is>
-          <t>Al Salam Complex 3hrs + Adil Villa 5hrs</t>
+          <t>Adil Villa 5hrs + Al Salam Complex 3hrs</t>
         </is>
       </c>
       <c r="I23" s="28">
@@ -3346,9 +3360,9 @@
       <c r="A27" s="61" t="n">
         <v>46102</v>
       </c>
-      <c r="B27" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B27" s="76" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C27" s="68" t="n">
@@ -3465,7 +3479,7 @@
       </c>
       <c r="H30" s="75" t="inlineStr">
         <is>
-          <t>Saqia 14 (Store) 4hrs + Adil Villa 4hrs</t>
+          <t>Adil Villa 4hrs + Saqia 14 (Store) 4hrs</t>
         </is>
       </c>
       <c r="I30" s="34">
@@ -3499,7 +3513,7 @@
       </c>
       <c r="H31" s="69" t="inlineStr">
         <is>
-          <t>Al Salam Complex 4hrs + Adil Villa 4hrs</t>
+          <t>Adil Villa 4hrs + Al Salam Complex 4hrs</t>
         </is>
       </c>
       <c r="I31" s="28">
@@ -3584,9 +3598,9 @@
       <c r="A34" s="62" t="n">
         <v>46109</v>
       </c>
-      <c r="B34" s="76" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B34" s="77" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C34" s="72" t="n">
@@ -3652,7 +3666,7 @@
       <c r="A36" s="62" t="n">
         <v>46111</v>
       </c>
-      <c r="B36" s="76" t="inlineStr">
+      <c r="B36" s="78" t="inlineStr">
         <is>
           <t>V</t>
         </is>
@@ -3708,31 +3722,31 @@
           <t>إجمالي عدد الساعات :</t>
         </is>
       </c>
-      <c r="B38" s="77" t="n"/>
-      <c r="C38" s="78">
+      <c r="B38" s="79" t="n"/>
+      <c r="C38" s="80">
         <f>SUM(C7:C37) -  (COUNTIF(B7:B37, "AWO") * 8)</f>
         <v/>
       </c>
-      <c r="D38" s="79">
+      <c r="D38" s="81">
         <f>IFERROR(SUM(D7:D37), "")</f>
         <v/>
       </c>
-      <c r="E38" s="79">
+      <c r="E38" s="81">
         <f>IFERROR(SUM(E7:E37), "")</f>
         <v/>
       </c>
-      <c r="F38" s="79">
+      <c r="F38" s="81">
         <f>IFERROR(SUM(F7:F37), "")</f>
         <v/>
       </c>
       <c r="G38" s="13" t="n"/>
-      <c r="H38" s="80" t="n"/>
+      <c r="H38" s="82" t="n"/>
       <c r="I38" s="32" t="inlineStr">
         <is>
           <t>الملاحظات :</t>
         </is>
       </c>
-      <c r="J38" s="81" t="n"/>
+      <c r="J38" s="83" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1" s="44">
       <c r="A39" s="54" t="inlineStr">
@@ -3740,20 +3754,20 @@
           <t>إجمالي عدد ايام الدوام :</t>
         </is>
       </c>
-      <c r="B39" s="77" t="n"/>
-      <c r="C39" s="82">
+      <c r="B39" s="79" t="n"/>
+      <c r="C39" s="84">
         <f>COUNTIF(B7:B37, "P") + COUNTIF(B7:B37, "W") + COUNTIF(B7:B37, "H") + COUNTIF(B7:B37, "A") + COUNTIF(B7:B37, "AWO")-C40</f>
         <v/>
       </c>
-      <c r="D39" s="82" t="n"/>
-      <c r="E39" s="82" t="n"/>
-      <c r="F39" s="82" t="n"/>
+      <c r="D39" s="84" t="n"/>
+      <c r="E39" s="84" t="n"/>
+      <c r="F39" s="84" t="n"/>
       <c r="G39" s="35" t="inlineStr">
         <is>
           <t>الاجازات المرضية</t>
         </is>
       </c>
-      <c r="H39" s="83">
+      <c r="H39" s="85">
         <f>COUNTIF(B7:B37,"sl")</f>
         <v/>
       </c>
@@ -3761,7 +3775,7 @@
         <f>COUNTIFS(G7:G37, "SL", G7:G37, "&lt;=3")</f>
         <v/>
       </c>
-      <c r="J39" s="81" t="n"/>
+      <c r="J39" s="83" t="n"/>
     </row>
     <row r="40" ht="37.2" customHeight="1" s="44">
       <c r="A40" s="54" t="inlineStr">
@@ -3769,24 +3783,24 @@
           <t>إجمالي عدد ايام الغياب :</t>
         </is>
       </c>
-      <c r="B40" s="77" t="n"/>
-      <c r="C40" s="82">
+      <c r="B40" s="79" t="n"/>
+      <c r="C40" s="84">
         <f>COUNTIF(B7:B37,"A")+COUNTIF(B7:B37,"AWO")*2</f>
         <v/>
       </c>
-      <c r="D40" s="82" t="n"/>
-      <c r="E40" s="82" t="n"/>
-      <c r="F40" s="82" t="n"/>
+      <c r="D40" s="84" t="n"/>
+      <c r="E40" s="84" t="n"/>
+      <c r="F40" s="84" t="n"/>
       <c r="G40" s="33" t="inlineStr">
         <is>
           <t>قيمة الخصم الاضافي</t>
         </is>
       </c>
-      <c r="H40" s="84" t="n">
+      <c r="H40" s="86" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="47" t="n"/>
-      <c r="J40" s="81" t="n"/>
+      <c r="J40" s="83" t="n"/>
     </row>
     <row r="41" ht="37.2" customHeight="1" s="44">
       <c r="A41" s="54" t="inlineStr">
@@ -3794,25 +3808,25 @@
           <t>قيمة الخصم :</t>
         </is>
       </c>
-      <c r="B41" s="77" t="n"/>
-      <c r="C41" s="85">
+      <c r="B41" s="79" t="n"/>
+      <c r="C41" s="87">
         <f>COUNTIF(B7:B37,"AWO") * 2 * I3 +COUNTIF(B7:B37, "A") * I3</f>
         <v/>
       </c>
-      <c r="D41" s="82" t="n"/>
-      <c r="E41" s="82" t="n"/>
-      <c r="F41" s="86" t="n"/>
+      <c r="D41" s="84" t="n"/>
+      <c r="E41" s="84" t="n"/>
+      <c r="F41" s="88" t="n"/>
       <c r="G41" s="35" t="inlineStr">
         <is>
           <t>مجموع الخصم :</t>
         </is>
       </c>
-      <c r="H41" s="84">
+      <c r="H41" s="86">
         <f>SUM(C41+H40)</f>
         <v/>
       </c>
       <c r="I41" s="48" t="n"/>
-      <c r="J41" s="81" t="n"/>
+      <c r="J41" s="83" t="n"/>
     </row>
     <row r="42" ht="37.2" customHeight="1" s="44">
       <c r="A42" s="54" t="inlineStr">
@@ -3820,20 +3834,20 @@
           <t>إجمالي الأجر بعد الخصم :</t>
         </is>
       </c>
-      <c r="B42" s="77" t="n"/>
-      <c r="C42" s="87">
+      <c r="B42" s="79" t="n"/>
+      <c r="C42" s="89">
         <f>IF(F4&lt;&gt;"", I2/(DAY(EOMONTH(F2,0))*8)*C38, "")</f>
         <v/>
       </c>
-      <c r="D42" s="87">
+      <c r="D42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*1.25*D38, "")</f>
         <v/>
       </c>
-      <c r="E42" s="87">
+      <c r="E42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*1.5*E38, "")</f>
         <v/>
       </c>
-      <c r="F42" s="87">
+      <c r="F42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*2.5*F38, "")</f>
         <v/>
       </c>
@@ -3842,12 +3856,12 @@
           <t>: الإجمالي</t>
         </is>
       </c>
-      <c r="H42" s="77" t="n"/>
+      <c r="H42" s="79" t="n"/>
       <c r="I42" s="67">
         <f>IFERROR(SUM(C42:F42), "") - H40</f>
         <v/>
       </c>
-      <c r="J42" s="81" t="n"/>
+      <c r="J42" s="83" t="n"/>
     </row>
     <row r="43" ht="34.2" customHeight="1" s="44">
       <c r="A43" s="17" t="inlineStr">
@@ -3855,86 +3869,86 @@
           <t xml:space="preserve">التاريخ : </t>
         </is>
       </c>
-      <c r="B43" s="88">
+      <c r="B43" s="90">
         <f>TODAY()</f>
         <v/>
       </c>
-      <c r="C43" s="89" t="n"/>
-      <c r="D43" s="90" t="inlineStr">
+      <c r="C43" s="91" t="n"/>
+      <c r="D43" s="92" t="inlineStr">
         <is>
           <t xml:space="preserve">توقيع الموظف : </t>
         </is>
       </c>
-      <c r="E43" s="90" t="n"/>
-      <c r="F43" s="90" t="n"/>
+      <c r="E43" s="92" t="n"/>
+      <c r="F43" s="92" t="n"/>
       <c r="G43" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">توقيع المدير : </t>
         </is>
       </c>
-      <c r="H43" s="91" t="n"/>
+      <c r="H43" s="93" t="n"/>
       <c r="I43" s="18" t="n"/>
-      <c r="J43" s="81" t="n"/>
+      <c r="J43" s="83" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="19" t="n"/>
-      <c r="B44" s="92" t="n"/>
-      <c r="C44" s="92" t="n"/>
-      <c r="D44" s="92" t="n"/>
-      <c r="E44" s="92" t="n"/>
-      <c r="F44" s="92" t="n"/>
+      <c r="B44" s="94" t="n"/>
+      <c r="C44" s="94" t="n"/>
+      <c r="D44" s="94" t="n"/>
+      <c r="E44" s="94" t="n"/>
+      <c r="F44" s="94" t="n"/>
       <c r="G44" s="19" t="n"/>
-      <c r="H44" s="92" t="n"/>
+      <c r="H44" s="94" t="n"/>
       <c r="I44" s="19" t="n"/>
-      <c r="J44" s="81" t="n"/>
+      <c r="J44" s="83" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="19" t="n"/>
-      <c r="B45" s="92" t="n"/>
-      <c r="C45" s="92" t="n"/>
-      <c r="D45" s="92" t="n"/>
-      <c r="E45" s="92" t="n"/>
-      <c r="F45" s="92" t="n"/>
+      <c r="B45" s="94" t="n"/>
+      <c r="C45" s="94" t="n"/>
+      <c r="D45" s="94" t="n"/>
+      <c r="E45" s="94" t="n"/>
+      <c r="F45" s="94" t="n"/>
       <c r="G45" s="19" t="n"/>
-      <c r="H45" s="92" t="n"/>
+      <c r="H45" s="94" t="n"/>
       <c r="I45" s="19" t="n"/>
-      <c r="J45" s="81" t="n"/>
+      <c r="J45" s="83" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="81" t="n"/>
-      <c r="C46" s="81" t="n"/>
-      <c r="D46" s="81" t="n"/>
-      <c r="E46" s="81" t="n"/>
-      <c r="F46" s="81" t="n"/>
-      <c r="H46" s="81" t="n"/>
-      <c r="J46" s="81" t="n"/>
+      <c r="B46" s="83" t="n"/>
+      <c r="C46" s="83" t="n"/>
+      <c r="D46" s="83" t="n"/>
+      <c r="E46" s="83" t="n"/>
+      <c r="F46" s="83" t="n"/>
+      <c r="H46" s="83" t="n"/>
+      <c r="J46" s="83" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="81" t="n"/>
-      <c r="C47" s="81" t="n"/>
-      <c r="D47" s="81" t="n"/>
-      <c r="E47" s="81" t="n"/>
-      <c r="F47" s="81" t="n"/>
-      <c r="H47" s="81" t="n"/>
-      <c r="J47" s="81" t="n"/>
+      <c r="B47" s="83" t="n"/>
+      <c r="C47" s="83" t="n"/>
+      <c r="D47" s="83" t="n"/>
+      <c r="E47" s="83" t="n"/>
+      <c r="F47" s="83" t="n"/>
+      <c r="H47" s="83" t="n"/>
+      <c r="J47" s="83" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="81" t="n"/>
-      <c r="C48" s="81" t="n"/>
-      <c r="D48" s="81" t="n"/>
-      <c r="E48" s="81" t="n"/>
-      <c r="F48" s="81" t="n"/>
-      <c r="H48" s="81" t="n"/>
-      <c r="J48" s="81" t="n"/>
+      <c r="B48" s="83" t="n"/>
+      <c r="C48" s="83" t="n"/>
+      <c r="D48" s="83" t="n"/>
+      <c r="E48" s="83" t="n"/>
+      <c r="F48" s="83" t="n"/>
+      <c r="H48" s="83" t="n"/>
+      <c r="J48" s="83" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="81" t="n"/>
-      <c r="C49" s="81" t="n"/>
-      <c r="D49" s="81" t="n"/>
-      <c r="E49" s="81" t="n"/>
-      <c r="F49" s="81" t="n"/>
-      <c r="H49" s="81" t="n"/>
-      <c r="J49" s="81" t="n"/>
+      <c r="B49" s="83" t="n"/>
+      <c r="C49" s="83" t="n"/>
+      <c r="D49" s="83" t="n"/>
+      <c r="E49" s="83" t="n"/>
+      <c r="F49" s="83" t="n"/>
+      <c r="H49" s="83" t="n"/>
+      <c r="J49" s="83" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="45">
@@ -4356,9 +4370,9 @@
       <c r="A13" s="62" t="n">
         <v>46088</v>
       </c>
-      <c r="B13" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B13" s="76" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C13" s="68" t="n">
@@ -4596,9 +4610,9 @@
       <c r="A20" s="62" t="n">
         <v>46095</v>
       </c>
-      <c r="B20" s="71" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B20" s="76" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C20" s="72" t="n">
@@ -4836,9 +4850,9 @@
       <c r="A27" s="61" t="n">
         <v>46102</v>
       </c>
-      <c r="B27" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B27" s="76" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C27" s="68" t="n">
@@ -5074,9 +5088,9 @@
       <c r="A34" s="62" t="n">
         <v>46109</v>
       </c>
-      <c r="B34" s="76" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B34" s="77" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C34" s="72" t="n">
@@ -5142,7 +5156,7 @@
       <c r="A36" s="62" t="n">
         <v>46111</v>
       </c>
-      <c r="B36" s="76" t="inlineStr">
+      <c r="B36" s="78" t="inlineStr">
         <is>
           <t>P</t>
         </is>
@@ -5206,31 +5220,31 @@
           <t>إجمالي عدد الساعات :</t>
         </is>
       </c>
-      <c r="B38" s="77" t="n"/>
-      <c r="C38" s="78">
+      <c r="B38" s="79" t="n"/>
+      <c r="C38" s="80">
         <f>SUM(C7:C37) -  (COUNTIF(B7:B37, "AWO") * 8)</f>
         <v/>
       </c>
-      <c r="D38" s="79">
+      <c r="D38" s="81">
         <f>IFERROR(SUM(D7:D37), "")</f>
         <v/>
       </c>
-      <c r="E38" s="79">
+      <c r="E38" s="81">
         <f>IFERROR(SUM(E7:E37), "")</f>
         <v/>
       </c>
-      <c r="F38" s="79">
+      <c r="F38" s="81">
         <f>IFERROR(SUM(F7:F37), "")</f>
         <v/>
       </c>
       <c r="G38" s="13" t="n"/>
-      <c r="H38" s="80" t="n"/>
+      <c r="H38" s="82" t="n"/>
       <c r="I38" s="32" t="inlineStr">
         <is>
           <t>الملاحظات :</t>
         </is>
       </c>
-      <c r="J38" s="81" t="n"/>
+      <c r="J38" s="83" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1" s="44">
       <c r="A39" s="54" t="inlineStr">
@@ -5238,20 +5252,20 @@
           <t>إجمالي عدد ايام الدوام :</t>
         </is>
       </c>
-      <c r="B39" s="77" t="n"/>
-      <c r="C39" s="82">
+      <c r="B39" s="79" t="n"/>
+      <c r="C39" s="84">
         <f>COUNTIF(B7:B37, "P") + COUNTIF(B7:B37, "W") + COUNTIF(B7:B37, "H") + COUNTIF(B7:B37, "A") + COUNTIF(B7:B37, "AWO")-C40</f>
         <v/>
       </c>
-      <c r="D39" s="82" t="n"/>
-      <c r="E39" s="82" t="n"/>
-      <c r="F39" s="82" t="n"/>
+      <c r="D39" s="84" t="n"/>
+      <c r="E39" s="84" t="n"/>
+      <c r="F39" s="84" t="n"/>
       <c r="G39" s="35" t="inlineStr">
         <is>
           <t>الاجازات المرضية</t>
         </is>
       </c>
-      <c r="H39" s="83">
+      <c r="H39" s="85">
         <f>COUNTIF(B7:B37,"sl")</f>
         <v/>
       </c>
@@ -5259,7 +5273,7 @@
         <f>COUNTIFS(G7:G37, "SL", G7:G37, "&lt;=3")</f>
         <v/>
       </c>
-      <c r="J39" s="81" t="n"/>
+      <c r="J39" s="83" t="n"/>
     </row>
     <row r="40" ht="37.2" customHeight="1" s="44">
       <c r="A40" s="54" t="inlineStr">
@@ -5267,24 +5281,24 @@
           <t>إجمالي عدد ايام الغياب :</t>
         </is>
       </c>
-      <c r="B40" s="77" t="n"/>
-      <c r="C40" s="82">
+      <c r="B40" s="79" t="n"/>
+      <c r="C40" s="84">
         <f>COUNTIF(B7:B37,"A")+COUNTIF(B7:B37,"AWO")*2</f>
         <v/>
       </c>
-      <c r="D40" s="82" t="n"/>
-      <c r="E40" s="82" t="n"/>
-      <c r="F40" s="82" t="n"/>
+      <c r="D40" s="84" t="n"/>
+      <c r="E40" s="84" t="n"/>
+      <c r="F40" s="84" t="n"/>
       <c r="G40" s="33" t="inlineStr">
         <is>
           <t>قيمة الخصم الاضافي</t>
         </is>
       </c>
-      <c r="H40" s="84" t="n">
+      <c r="H40" s="86" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="47" t="n"/>
-      <c r="J40" s="81" t="n"/>
+      <c r="J40" s="83" t="n"/>
     </row>
     <row r="41" ht="37.2" customHeight="1" s="44">
       <c r="A41" s="54" t="inlineStr">
@@ -5292,25 +5306,25 @@
           <t>قيمة الخصم :</t>
         </is>
       </c>
-      <c r="B41" s="77" t="n"/>
-      <c r="C41" s="85">
+      <c r="B41" s="79" t="n"/>
+      <c r="C41" s="87">
         <f>COUNTIF(B7:B37,"AWO") * 2 * I3 +COUNTIF(B7:B37, "A") * I3</f>
         <v/>
       </c>
-      <c r="D41" s="82" t="n"/>
-      <c r="E41" s="82" t="n"/>
-      <c r="F41" s="86" t="n"/>
+      <c r="D41" s="84" t="n"/>
+      <c r="E41" s="84" t="n"/>
+      <c r="F41" s="88" t="n"/>
       <c r="G41" s="35" t="inlineStr">
         <is>
           <t>مجموع الخصم :</t>
         </is>
       </c>
-      <c r="H41" s="84">
+      <c r="H41" s="86">
         <f>SUM(C41+H40)</f>
         <v/>
       </c>
       <c r="I41" s="48" t="n"/>
-      <c r="J41" s="81" t="n"/>
+      <c r="J41" s="83" t="n"/>
     </row>
     <row r="42" ht="37.2" customHeight="1" s="44">
       <c r="A42" s="54" t="inlineStr">
@@ -5318,20 +5332,20 @@
           <t>إجمالي الأجر بعد الخصم :</t>
         </is>
       </c>
-      <c r="B42" s="77" t="n"/>
-      <c r="C42" s="87">
+      <c r="B42" s="79" t="n"/>
+      <c r="C42" s="89">
         <f>IF(F4&lt;&gt;"", I2/(DAY(EOMONTH(F2,0))*8)*C38, "")</f>
         <v/>
       </c>
-      <c r="D42" s="87">
+      <c r="D42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*1.25*D38, "")</f>
         <v/>
       </c>
-      <c r="E42" s="87">
+      <c r="E42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*1.5*E38, "")</f>
         <v/>
       </c>
-      <c r="F42" s="87">
+      <c r="F42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*2.5*F38, "")</f>
         <v/>
       </c>
@@ -5340,12 +5354,12 @@
           <t>: الإجمالي</t>
         </is>
       </c>
-      <c r="H42" s="77" t="n"/>
+      <c r="H42" s="79" t="n"/>
       <c r="I42" s="67">
         <f>IFERROR(SUM(C42:F42), "") - H40</f>
         <v/>
       </c>
-      <c r="J42" s="81" t="n"/>
+      <c r="J42" s="83" t="n"/>
     </row>
     <row r="43" ht="34.2" customHeight="1" s="44">
       <c r="A43" s="17" t="inlineStr">
@@ -5353,86 +5367,86 @@
           <t xml:space="preserve">التاريخ : </t>
         </is>
       </c>
-      <c r="B43" s="88">
+      <c r="B43" s="90">
         <f>TODAY()</f>
         <v/>
       </c>
-      <c r="C43" s="89" t="n"/>
-      <c r="D43" s="90" t="inlineStr">
+      <c r="C43" s="91" t="n"/>
+      <c r="D43" s="92" t="inlineStr">
         <is>
           <t xml:space="preserve">توقيع الموظف : </t>
         </is>
       </c>
-      <c r="E43" s="90" t="n"/>
-      <c r="F43" s="90" t="n"/>
+      <c r="E43" s="92" t="n"/>
+      <c r="F43" s="92" t="n"/>
       <c r="G43" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">توقيع المدير : </t>
         </is>
       </c>
-      <c r="H43" s="91" t="n"/>
+      <c r="H43" s="93" t="n"/>
       <c r="I43" s="18" t="n"/>
-      <c r="J43" s="81" t="n"/>
+      <c r="J43" s="83" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="19" t="n"/>
-      <c r="B44" s="92" t="n"/>
-      <c r="C44" s="92" t="n"/>
-      <c r="D44" s="92" t="n"/>
-      <c r="E44" s="92" t="n"/>
-      <c r="F44" s="92" t="n"/>
+      <c r="B44" s="94" t="n"/>
+      <c r="C44" s="94" t="n"/>
+      <c r="D44" s="94" t="n"/>
+      <c r="E44" s="94" t="n"/>
+      <c r="F44" s="94" t="n"/>
       <c r="G44" s="19" t="n"/>
-      <c r="H44" s="92" t="n"/>
+      <c r="H44" s="94" t="n"/>
       <c r="I44" s="19" t="n"/>
-      <c r="J44" s="81" t="n"/>
+      <c r="J44" s="83" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="19" t="n"/>
-      <c r="B45" s="92" t="n"/>
-      <c r="C45" s="92" t="n"/>
-      <c r="D45" s="92" t="n"/>
-      <c r="E45" s="92" t="n"/>
-      <c r="F45" s="92" t="n"/>
+      <c r="B45" s="94" t="n"/>
+      <c r="C45" s="94" t="n"/>
+      <c r="D45" s="94" t="n"/>
+      <c r="E45" s="94" t="n"/>
+      <c r="F45" s="94" t="n"/>
       <c r="G45" s="19" t="n"/>
-      <c r="H45" s="92" t="n"/>
+      <c r="H45" s="94" t="n"/>
       <c r="I45" s="19" t="n"/>
-      <c r="J45" s="81" t="n"/>
+      <c r="J45" s="83" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="81" t="n"/>
-      <c r="C46" s="81" t="n"/>
-      <c r="D46" s="81" t="n"/>
-      <c r="E46" s="81" t="n"/>
-      <c r="F46" s="81" t="n"/>
-      <c r="H46" s="81" t="n"/>
-      <c r="J46" s="81" t="n"/>
+      <c r="B46" s="83" t="n"/>
+      <c r="C46" s="83" t="n"/>
+      <c r="D46" s="83" t="n"/>
+      <c r="E46" s="83" t="n"/>
+      <c r="F46" s="83" t="n"/>
+      <c r="H46" s="83" t="n"/>
+      <c r="J46" s="83" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="81" t="n"/>
-      <c r="C47" s="81" t="n"/>
-      <c r="D47" s="81" t="n"/>
-      <c r="E47" s="81" t="n"/>
-      <c r="F47" s="81" t="n"/>
-      <c r="H47" s="81" t="n"/>
-      <c r="J47" s="81" t="n"/>
+      <c r="B47" s="83" t="n"/>
+      <c r="C47" s="83" t="n"/>
+      <c r="D47" s="83" t="n"/>
+      <c r="E47" s="83" t="n"/>
+      <c r="F47" s="83" t="n"/>
+      <c r="H47" s="83" t="n"/>
+      <c r="J47" s="83" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="81" t="n"/>
-      <c r="C48" s="81" t="n"/>
-      <c r="D48" s="81" t="n"/>
-      <c r="E48" s="81" t="n"/>
-      <c r="F48" s="81" t="n"/>
-      <c r="H48" s="81" t="n"/>
-      <c r="J48" s="81" t="n"/>
+      <c r="B48" s="83" t="n"/>
+      <c r="C48" s="83" t="n"/>
+      <c r="D48" s="83" t="n"/>
+      <c r="E48" s="83" t="n"/>
+      <c r="F48" s="83" t="n"/>
+      <c r="H48" s="83" t="n"/>
+      <c r="J48" s="83" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="81" t="n"/>
-      <c r="C49" s="81" t="n"/>
-      <c r="D49" s="81" t="n"/>
-      <c r="E49" s="81" t="n"/>
-      <c r="F49" s="81" t="n"/>
-      <c r="H49" s="81" t="n"/>
-      <c r="J49" s="81" t="n"/>
+      <c r="B49" s="83" t="n"/>
+      <c r="C49" s="83" t="n"/>
+      <c r="D49" s="83" t="n"/>
+      <c r="E49" s="83" t="n"/>
+      <c r="F49" s="83" t="n"/>
+      <c r="H49" s="83" t="n"/>
+      <c r="J49" s="83" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="45">
@@ -5856,9 +5870,9 @@
       <c r="A13" s="62" t="n">
         <v>46088</v>
       </c>
-      <c r="B13" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B13" s="76" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C13" s="68" t="n">
@@ -6098,9 +6112,9 @@
       <c r="A20" s="62" t="n">
         <v>46095</v>
       </c>
-      <c r="B20" s="71" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B20" s="76" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C20" s="72" t="n">
@@ -6202,9 +6216,11 @@
         </is>
       </c>
       <c r="C23" s="68" t="n">
-        <v>7</v>
-      </c>
-      <c r="D23" s="68" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="D23" s="68" t="n">
+        <v>1</v>
+      </c>
       <c r="E23" s="68" t="n"/>
       <c r="F23" s="68" t="n"/>
       <c r="G23" s="26">
@@ -6213,7 +6229,7 @@
       </c>
       <c r="H23" s="69" t="inlineStr">
         <is>
-          <t>Adil Villa -1hrs + Al Salam Complex 8hrs</t>
+          <t>Adil Villa 0hrs + Al Salam Complex 8hrs</t>
         </is>
       </c>
       <c r="I23" s="28">
@@ -6530,7 +6546,7 @@
       <c r="A34" s="62" t="n">
         <v>46109</v>
       </c>
-      <c r="B34" s="76" t="inlineStr">
+      <c r="B34" s="78" t="inlineStr">
         <is>
           <t>V</t>
         </is>
@@ -6590,7 +6606,7 @@
       <c r="A36" s="62" t="n">
         <v>46111</v>
       </c>
-      <c r="B36" s="76" t="inlineStr">
+      <c r="B36" s="78" t="inlineStr">
         <is>
           <t>V</t>
         </is>
@@ -6646,31 +6662,31 @@
           <t>إجمالي عدد الساعات :</t>
         </is>
       </c>
-      <c r="B38" s="77" t="n"/>
-      <c r="C38" s="78">
+      <c r="B38" s="79" t="n"/>
+      <c r="C38" s="80">
         <f>SUM(C7:C37) -  (COUNTIF(B7:B37, "AWO") * 8)</f>
         <v/>
       </c>
-      <c r="D38" s="79">
+      <c r="D38" s="81">
         <f>IFERROR(SUM(D7:D37), "")</f>
         <v/>
       </c>
-      <c r="E38" s="79">
+      <c r="E38" s="81">
         <f>IFERROR(SUM(E7:E37), "")</f>
         <v/>
       </c>
-      <c r="F38" s="79">
+      <c r="F38" s="81">
         <f>IFERROR(SUM(F7:F37), "")</f>
         <v/>
       </c>
       <c r="G38" s="13" t="n"/>
-      <c r="H38" s="80" t="n"/>
+      <c r="H38" s="82" t="n"/>
       <c r="I38" s="32" t="inlineStr">
         <is>
           <t>الملاحظات :</t>
         </is>
       </c>
-      <c r="J38" s="81" t="n"/>
+      <c r="J38" s="83" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1" s="44">
       <c r="A39" s="54" t="inlineStr">
@@ -6678,20 +6694,20 @@
           <t>إجمالي عدد ايام الدوام :</t>
         </is>
       </c>
-      <c r="B39" s="77" t="n"/>
-      <c r="C39" s="82">
+      <c r="B39" s="79" t="n"/>
+      <c r="C39" s="84">
         <f>COUNTIF(B7:B37, "P") + COUNTIF(B7:B37, "W") + COUNTIF(B7:B37, "H") + COUNTIF(B7:B37, "A") + COUNTIF(B7:B37, "AWO")-C40</f>
         <v/>
       </c>
-      <c r="D39" s="82" t="n"/>
-      <c r="E39" s="82" t="n"/>
-      <c r="F39" s="82" t="n"/>
+      <c r="D39" s="84" t="n"/>
+      <c r="E39" s="84" t="n"/>
+      <c r="F39" s="84" t="n"/>
       <c r="G39" s="35" t="inlineStr">
         <is>
           <t>الاجازات المرضية</t>
         </is>
       </c>
-      <c r="H39" s="83">
+      <c r="H39" s="85">
         <f>COUNTIF(B7:B37,"sl")</f>
         <v/>
       </c>
@@ -6699,7 +6715,7 @@
         <f>COUNTIFS(G7:G37, "SL", G7:G37, "&lt;=3")</f>
         <v/>
       </c>
-      <c r="J39" s="81" t="n"/>
+      <c r="J39" s="83" t="n"/>
     </row>
     <row r="40" ht="37.2" customHeight="1" s="44">
       <c r="A40" s="54" t="inlineStr">
@@ -6707,24 +6723,24 @@
           <t>إجمالي عدد ايام الغياب :</t>
         </is>
       </c>
-      <c r="B40" s="77" t="n"/>
-      <c r="C40" s="82">
+      <c r="B40" s="79" t="n"/>
+      <c r="C40" s="84">
         <f>COUNTIF(B7:B37,"A")+COUNTIF(B7:B37,"AWO")*2</f>
         <v/>
       </c>
-      <c r="D40" s="82" t="n"/>
-      <c r="E40" s="82" t="n"/>
-      <c r="F40" s="82" t="n"/>
+      <c r="D40" s="84" t="n"/>
+      <c r="E40" s="84" t="n"/>
+      <c r="F40" s="84" t="n"/>
       <c r="G40" s="33" t="inlineStr">
         <is>
           <t>قيمة الخصم الاضافي</t>
         </is>
       </c>
-      <c r="H40" s="84" t="n">
+      <c r="H40" s="86" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="47" t="n"/>
-      <c r="J40" s="81" t="n"/>
+      <c r="J40" s="83" t="n"/>
     </row>
     <row r="41" ht="37.2" customHeight="1" s="44">
       <c r="A41" s="54" t="inlineStr">
@@ -6732,25 +6748,25 @@
           <t>قيمة الخصم :</t>
         </is>
       </c>
-      <c r="B41" s="77" t="n"/>
-      <c r="C41" s="85">
+      <c r="B41" s="79" t="n"/>
+      <c r="C41" s="87">
         <f>COUNTIF(B7:B37,"AWO") * 2 * I3 +COUNTIF(B7:B37, "A") * I3</f>
         <v/>
       </c>
-      <c r="D41" s="82" t="n"/>
-      <c r="E41" s="82" t="n"/>
-      <c r="F41" s="86" t="n"/>
+      <c r="D41" s="84" t="n"/>
+      <c r="E41" s="84" t="n"/>
+      <c r="F41" s="88" t="n"/>
       <c r="G41" s="35" t="inlineStr">
         <is>
           <t>مجموع الخصم :</t>
         </is>
       </c>
-      <c r="H41" s="84">
+      <c r="H41" s="86">
         <f>SUM(C41+H40)</f>
         <v/>
       </c>
       <c r="I41" s="48" t="n"/>
-      <c r="J41" s="81" t="n"/>
+      <c r="J41" s="83" t="n"/>
     </row>
     <row r="42" ht="37.2" customHeight="1" s="44">
       <c r="A42" s="54" t="inlineStr">
@@ -6758,20 +6774,20 @@
           <t>إجمالي الأجر بعد الخصم :</t>
         </is>
       </c>
-      <c r="B42" s="77" t="n"/>
-      <c r="C42" s="87">
+      <c r="B42" s="79" t="n"/>
+      <c r="C42" s="89">
         <f>IF(F4&lt;&gt;"", I2/(DAY(EOMONTH(F2,0))*8)*C38, "")</f>
         <v/>
       </c>
-      <c r="D42" s="87">
+      <c r="D42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*1.25*D38, "")</f>
         <v/>
       </c>
-      <c r="E42" s="87">
+      <c r="E42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*1.5*E38, "")</f>
         <v/>
       </c>
-      <c r="F42" s="87">
+      <c r="F42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*2.5*F38, "")</f>
         <v/>
       </c>
@@ -6780,12 +6796,12 @@
           <t>: الإجمالي</t>
         </is>
       </c>
-      <c r="H42" s="77" t="n"/>
+      <c r="H42" s="79" t="n"/>
       <c r="I42" s="67">
         <f>IFERROR(SUM(C42:F42), "") - H40</f>
         <v/>
       </c>
-      <c r="J42" s="81" t="n"/>
+      <c r="J42" s="83" t="n"/>
     </row>
     <row r="43" ht="34.2" customHeight="1" s="44">
       <c r="A43" s="17" t="inlineStr">
@@ -6793,86 +6809,86 @@
           <t xml:space="preserve">التاريخ : </t>
         </is>
       </c>
-      <c r="B43" s="88">
+      <c r="B43" s="90">
         <f>TODAY()</f>
         <v/>
       </c>
-      <c r="C43" s="89" t="n"/>
-      <c r="D43" s="90" t="inlineStr">
+      <c r="C43" s="91" t="n"/>
+      <c r="D43" s="92" t="inlineStr">
         <is>
           <t xml:space="preserve">توقيع الموظف : </t>
         </is>
       </c>
-      <c r="E43" s="90" t="n"/>
-      <c r="F43" s="90" t="n"/>
+      <c r="E43" s="92" t="n"/>
+      <c r="F43" s="92" t="n"/>
       <c r="G43" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">توقيع المدير : </t>
         </is>
       </c>
-      <c r="H43" s="91" t="n"/>
+      <c r="H43" s="93" t="n"/>
       <c r="I43" s="18" t="n"/>
-      <c r="J43" s="81" t="n"/>
+      <c r="J43" s="83" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="19" t="n"/>
-      <c r="B44" s="92" t="n"/>
-      <c r="C44" s="92" t="n"/>
-      <c r="D44" s="92" t="n"/>
-      <c r="E44" s="92" t="n"/>
-      <c r="F44" s="92" t="n"/>
+      <c r="B44" s="94" t="n"/>
+      <c r="C44" s="94" t="n"/>
+      <c r="D44" s="94" t="n"/>
+      <c r="E44" s="94" t="n"/>
+      <c r="F44" s="94" t="n"/>
       <c r="G44" s="19" t="n"/>
-      <c r="H44" s="92" t="n"/>
+      <c r="H44" s="94" t="n"/>
       <c r="I44" s="19" t="n"/>
-      <c r="J44" s="81" t="n"/>
+      <c r="J44" s="83" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="19" t="n"/>
-      <c r="B45" s="92" t="n"/>
-      <c r="C45" s="92" t="n"/>
-      <c r="D45" s="92" t="n"/>
-      <c r="E45" s="92" t="n"/>
-      <c r="F45" s="92" t="n"/>
+      <c r="B45" s="94" t="n"/>
+      <c r="C45" s="94" t="n"/>
+      <c r="D45" s="94" t="n"/>
+      <c r="E45" s="94" t="n"/>
+      <c r="F45" s="94" t="n"/>
       <c r="G45" s="19" t="n"/>
-      <c r="H45" s="92" t="n"/>
+      <c r="H45" s="94" t="n"/>
       <c r="I45" s="19" t="n"/>
-      <c r="J45" s="81" t="n"/>
+      <c r="J45" s="83" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="81" t="n"/>
-      <c r="C46" s="81" t="n"/>
-      <c r="D46" s="81" t="n"/>
-      <c r="E46" s="81" t="n"/>
-      <c r="F46" s="81" t="n"/>
-      <c r="H46" s="81" t="n"/>
-      <c r="J46" s="81" t="n"/>
+      <c r="B46" s="83" t="n"/>
+      <c r="C46" s="83" t="n"/>
+      <c r="D46" s="83" t="n"/>
+      <c r="E46" s="83" t="n"/>
+      <c r="F46" s="83" t="n"/>
+      <c r="H46" s="83" t="n"/>
+      <c r="J46" s="83" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="81" t="n"/>
-      <c r="C47" s="81" t="n"/>
-      <c r="D47" s="81" t="n"/>
-      <c r="E47" s="81" t="n"/>
-      <c r="F47" s="81" t="n"/>
-      <c r="H47" s="81" t="n"/>
-      <c r="J47" s="81" t="n"/>
+      <c r="B47" s="83" t="n"/>
+      <c r="C47" s="83" t="n"/>
+      <c r="D47" s="83" t="n"/>
+      <c r="E47" s="83" t="n"/>
+      <c r="F47" s="83" t="n"/>
+      <c r="H47" s="83" t="n"/>
+      <c r="J47" s="83" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="81" t="n"/>
-      <c r="C48" s="81" t="n"/>
-      <c r="D48" s="81" t="n"/>
-      <c r="E48" s="81" t="n"/>
-      <c r="F48" s="81" t="n"/>
-      <c r="H48" s="81" t="n"/>
-      <c r="J48" s="81" t="n"/>
+      <c r="B48" s="83" t="n"/>
+      <c r="C48" s="83" t="n"/>
+      <c r="D48" s="83" t="n"/>
+      <c r="E48" s="83" t="n"/>
+      <c r="F48" s="83" t="n"/>
+      <c r="H48" s="83" t="n"/>
+      <c r="J48" s="83" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="81" t="n"/>
-      <c r="C49" s="81" t="n"/>
-      <c r="D49" s="81" t="n"/>
-      <c r="E49" s="81" t="n"/>
-      <c r="F49" s="81" t="n"/>
-      <c r="H49" s="81" t="n"/>
-      <c r="J49" s="81" t="n"/>
+      <c r="B49" s="83" t="n"/>
+      <c r="C49" s="83" t="n"/>
+      <c r="D49" s="83" t="n"/>
+      <c r="E49" s="83" t="n"/>
+      <c r="F49" s="83" t="n"/>
+      <c r="H49" s="83" t="n"/>
+      <c r="J49" s="83" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="45">
@@ -7294,9 +7310,9 @@
       <c r="A13" s="62" t="n">
         <v>46088</v>
       </c>
-      <c r="B13" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B13" s="76" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C13" s="68" t="n">
@@ -7534,9 +7550,9 @@
       <c r="A20" s="62" t="n">
         <v>46095</v>
       </c>
-      <c r="B20" s="71" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B20" s="76" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C20" s="72" t="n">
@@ -7653,7 +7669,7 @@
       </c>
       <c r="H23" s="69" t="inlineStr">
         <is>
-          <t>Adil Villa 5hrs + Al Salam Complex 3hrs</t>
+          <t>Al Salam Complex 3hrs + Adil Villa 5hrs</t>
         </is>
       </c>
       <c r="I23" s="28">
@@ -7772,9 +7788,9 @@
       <c r="A27" s="61" t="n">
         <v>46102</v>
       </c>
-      <c r="B27" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B27" s="76" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C27" s="68" t="n">
@@ -8010,9 +8026,9 @@
       <c r="A34" s="62" t="n">
         <v>46109</v>
       </c>
-      <c r="B34" s="76" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B34" s="77" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C34" s="72" t="n">
@@ -8078,7 +8094,7 @@
       <c r="A36" s="62" t="n">
         <v>46111</v>
       </c>
-      <c r="B36" s="76" t="inlineStr">
+      <c r="B36" s="78" t="inlineStr">
         <is>
           <t>P</t>
         </is>
@@ -8142,31 +8158,31 @@
           <t>إجمالي عدد الساعات :</t>
         </is>
       </c>
-      <c r="B38" s="77" t="n"/>
-      <c r="C38" s="78">
+      <c r="B38" s="79" t="n"/>
+      <c r="C38" s="80">
         <f>SUM(C7:C37) -  (COUNTIF(B7:B37, "AWO") * 8)</f>
         <v/>
       </c>
-      <c r="D38" s="79">
+      <c r="D38" s="81">
         <f>IFERROR(SUM(D7:D37), "")</f>
         <v/>
       </c>
-      <c r="E38" s="79">
+      <c r="E38" s="81">
         <f>IFERROR(SUM(E7:E37), "")</f>
         <v/>
       </c>
-      <c r="F38" s="79">
+      <c r="F38" s="81">
         <f>IFERROR(SUM(F7:F37), "")</f>
         <v/>
       </c>
       <c r="G38" s="13" t="n"/>
-      <c r="H38" s="80" t="n"/>
+      <c r="H38" s="82" t="n"/>
       <c r="I38" s="32" t="inlineStr">
         <is>
           <t>الملاحظات :</t>
         </is>
       </c>
-      <c r="J38" s="81" t="n"/>
+      <c r="J38" s="83" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1" s="44">
       <c r="A39" s="54" t="inlineStr">
@@ -8174,20 +8190,20 @@
           <t>إجمالي عدد ايام الدوام :</t>
         </is>
       </c>
-      <c r="B39" s="77" t="n"/>
-      <c r="C39" s="82">
+      <c r="B39" s="79" t="n"/>
+      <c r="C39" s="84">
         <f>COUNTIF(B7:B37, "P") + COUNTIF(B7:B37, "W") + COUNTIF(B7:B37, "H") + COUNTIF(B7:B37, "A") + COUNTIF(B7:B37, "AWO")-C40</f>
         <v/>
       </c>
-      <c r="D39" s="82" t="n"/>
-      <c r="E39" s="82" t="n"/>
-      <c r="F39" s="82" t="n"/>
+      <c r="D39" s="84" t="n"/>
+      <c r="E39" s="84" t="n"/>
+      <c r="F39" s="84" t="n"/>
       <c r="G39" s="35" t="inlineStr">
         <is>
           <t>الاجازات المرضية</t>
         </is>
       </c>
-      <c r="H39" s="83">
+      <c r="H39" s="85">
         <f>COUNTIF(B7:B37,"sl")</f>
         <v/>
       </c>
@@ -8195,7 +8211,7 @@
         <f>COUNTIFS(G7:G37, "SL", G7:G37, "&lt;=3")</f>
         <v/>
       </c>
-      <c r="J39" s="81" t="n"/>
+      <c r="J39" s="83" t="n"/>
     </row>
     <row r="40" ht="37.2" customHeight="1" s="44">
       <c r="A40" s="54" t="inlineStr">
@@ -8203,24 +8219,24 @@
           <t>إجمالي عدد ايام الغياب :</t>
         </is>
       </c>
-      <c r="B40" s="77" t="n"/>
-      <c r="C40" s="82">
+      <c r="B40" s="79" t="n"/>
+      <c r="C40" s="84">
         <f>COUNTIF(B7:B37,"A")+COUNTIF(B7:B37,"AWO")*2</f>
         <v/>
       </c>
-      <c r="D40" s="82" t="n"/>
-      <c r="E40" s="82" t="n"/>
-      <c r="F40" s="82" t="n"/>
+      <c r="D40" s="84" t="n"/>
+      <c r="E40" s="84" t="n"/>
+      <c r="F40" s="84" t="n"/>
       <c r="G40" s="33" t="inlineStr">
         <is>
           <t>قيمة الخصم الاضافي</t>
         </is>
       </c>
-      <c r="H40" s="84" t="n">
+      <c r="H40" s="86" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="47" t="n"/>
-      <c r="J40" s="81" t="n"/>
+      <c r="J40" s="83" t="n"/>
     </row>
     <row r="41" ht="37.2" customHeight="1" s="44">
       <c r="A41" s="54" t="inlineStr">
@@ -8228,25 +8244,25 @@
           <t>قيمة الخصم :</t>
         </is>
       </c>
-      <c r="B41" s="77" t="n"/>
-      <c r="C41" s="85">
+      <c r="B41" s="79" t="n"/>
+      <c r="C41" s="87">
         <f>COUNTIF(B7:B37,"AWO") * 2 * I3 +COUNTIF(B7:B37, "A") * I3</f>
         <v/>
       </c>
-      <c r="D41" s="82" t="n"/>
-      <c r="E41" s="82" t="n"/>
-      <c r="F41" s="86" t="n"/>
+      <c r="D41" s="84" t="n"/>
+      <c r="E41" s="84" t="n"/>
+      <c r="F41" s="88" t="n"/>
       <c r="G41" s="35" t="inlineStr">
         <is>
           <t>مجموع الخصم :</t>
         </is>
       </c>
-      <c r="H41" s="84">
+      <c r="H41" s="86">
         <f>SUM(C41+H40)</f>
         <v/>
       </c>
       <c r="I41" s="48" t="n"/>
-      <c r="J41" s="81" t="n"/>
+      <c r="J41" s="83" t="n"/>
     </row>
     <row r="42" ht="37.2" customHeight="1" s="44">
       <c r="A42" s="54" t="inlineStr">
@@ -8254,20 +8270,20 @@
           <t>إجمالي الأجر بعد الخصم :</t>
         </is>
       </c>
-      <c r="B42" s="77" t="n"/>
-      <c r="C42" s="87">
+      <c r="B42" s="79" t="n"/>
+      <c r="C42" s="89">
         <f>IF(F4&lt;&gt;"", I2/(DAY(EOMONTH(F2,0))*8)*C38, "")</f>
         <v/>
       </c>
-      <c r="D42" s="87">
+      <c r="D42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*1.25*D38, "")</f>
         <v/>
       </c>
-      <c r="E42" s="87">
+      <c r="E42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*1.5*E38, "")</f>
         <v/>
       </c>
-      <c r="F42" s="87">
+      <c r="F42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*2.5*F38, "")</f>
         <v/>
       </c>
@@ -8276,12 +8292,12 @@
           <t>: الإجمالي</t>
         </is>
       </c>
-      <c r="H42" s="77" t="n"/>
+      <c r="H42" s="79" t="n"/>
       <c r="I42" s="67">
         <f>IFERROR(SUM(C42:F42), "") - H40</f>
         <v/>
       </c>
-      <c r="J42" s="81" t="n"/>
+      <c r="J42" s="83" t="n"/>
     </row>
     <row r="43" ht="34.2" customHeight="1" s="44">
       <c r="A43" s="17" t="inlineStr">
@@ -8289,86 +8305,86 @@
           <t xml:space="preserve">التاريخ : </t>
         </is>
       </c>
-      <c r="B43" s="88">
+      <c r="B43" s="90">
         <f>TODAY()</f>
         <v/>
       </c>
-      <c r="C43" s="89" t="n"/>
-      <c r="D43" s="90" t="inlineStr">
+      <c r="C43" s="91" t="n"/>
+      <c r="D43" s="92" t="inlineStr">
         <is>
           <t xml:space="preserve">توقيع الموظف : </t>
         </is>
       </c>
-      <c r="E43" s="90" t="n"/>
-      <c r="F43" s="90" t="n"/>
+      <c r="E43" s="92" t="n"/>
+      <c r="F43" s="92" t="n"/>
       <c r="G43" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">توقيع المدير : </t>
         </is>
       </c>
-      <c r="H43" s="91" t="n"/>
+      <c r="H43" s="93" t="n"/>
       <c r="I43" s="18" t="n"/>
-      <c r="J43" s="81" t="n"/>
+      <c r="J43" s="83" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="19" t="n"/>
-      <c r="B44" s="92" t="n"/>
-      <c r="C44" s="92" t="n"/>
-      <c r="D44" s="92" t="n"/>
-      <c r="E44" s="92" t="n"/>
-      <c r="F44" s="92" t="n"/>
+      <c r="B44" s="94" t="n"/>
+      <c r="C44" s="94" t="n"/>
+      <c r="D44" s="94" t="n"/>
+      <c r="E44" s="94" t="n"/>
+      <c r="F44" s="94" t="n"/>
       <c r="G44" s="19" t="n"/>
-      <c r="H44" s="92" t="n"/>
+      <c r="H44" s="94" t="n"/>
       <c r="I44" s="19" t="n"/>
-      <c r="J44" s="81" t="n"/>
+      <c r="J44" s="83" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="19" t="n"/>
-      <c r="B45" s="92" t="n"/>
-      <c r="C45" s="92" t="n"/>
-      <c r="D45" s="92" t="n"/>
-      <c r="E45" s="92" t="n"/>
-      <c r="F45" s="92" t="n"/>
+      <c r="B45" s="94" t="n"/>
+      <c r="C45" s="94" t="n"/>
+      <c r="D45" s="94" t="n"/>
+      <c r="E45" s="94" t="n"/>
+      <c r="F45" s="94" t="n"/>
       <c r="G45" s="19" t="n"/>
-      <c r="H45" s="92" t="n"/>
+      <c r="H45" s="94" t="n"/>
       <c r="I45" s="19" t="n"/>
-      <c r="J45" s="81" t="n"/>
+      <c r="J45" s="83" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="81" t="n"/>
-      <c r="C46" s="81" t="n"/>
-      <c r="D46" s="81" t="n"/>
-      <c r="E46" s="81" t="n"/>
-      <c r="F46" s="81" t="n"/>
-      <c r="H46" s="81" t="n"/>
-      <c r="J46" s="81" t="n"/>
+      <c r="B46" s="83" t="n"/>
+      <c r="C46" s="83" t="n"/>
+      <c r="D46" s="83" t="n"/>
+      <c r="E46" s="83" t="n"/>
+      <c r="F46" s="83" t="n"/>
+      <c r="H46" s="83" t="n"/>
+      <c r="J46" s="83" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="81" t="n"/>
-      <c r="C47" s="81" t="n"/>
-      <c r="D47" s="81" t="n"/>
-      <c r="E47" s="81" t="n"/>
-      <c r="F47" s="81" t="n"/>
-      <c r="H47" s="81" t="n"/>
-      <c r="J47" s="81" t="n"/>
+      <c r="B47" s="83" t="n"/>
+      <c r="C47" s="83" t="n"/>
+      <c r="D47" s="83" t="n"/>
+      <c r="E47" s="83" t="n"/>
+      <c r="F47" s="83" t="n"/>
+      <c r="H47" s="83" t="n"/>
+      <c r="J47" s="83" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="81" t="n"/>
-      <c r="C48" s="81" t="n"/>
-      <c r="D48" s="81" t="n"/>
-      <c r="E48" s="81" t="n"/>
-      <c r="F48" s="81" t="n"/>
-      <c r="H48" s="81" t="n"/>
-      <c r="J48" s="81" t="n"/>
+      <c r="B48" s="83" t="n"/>
+      <c r="C48" s="83" t="n"/>
+      <c r="D48" s="83" t="n"/>
+      <c r="E48" s="83" t="n"/>
+      <c r="F48" s="83" t="n"/>
+      <c r="H48" s="83" t="n"/>
+      <c r="J48" s="83" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="81" t="n"/>
-      <c r="C49" s="81" t="n"/>
-      <c r="D49" s="81" t="n"/>
-      <c r="E49" s="81" t="n"/>
-      <c r="F49" s="81" t="n"/>
-      <c r="H49" s="81" t="n"/>
-      <c r="J49" s="81" t="n"/>
+      <c r="B49" s="83" t="n"/>
+      <c r="C49" s="83" t="n"/>
+      <c r="D49" s="83" t="n"/>
+      <c r="E49" s="83" t="n"/>
+      <c r="F49" s="83" t="n"/>
+      <c r="H49" s="83" t="n"/>
+      <c r="J49" s="83" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="45">
@@ -8792,9 +8808,9 @@
       <c r="A13" s="62" t="n">
         <v>46088</v>
       </c>
-      <c r="B13" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B13" s="76" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C13" s="68" t="n">
@@ -9034,9 +9050,9 @@
       <c r="A20" s="62" t="n">
         <v>46095</v>
       </c>
-      <c r="B20" s="71" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B20" s="76" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C20" s="72" t="n">
@@ -9276,9 +9292,9 @@
       <c r="A27" s="61" t="n">
         <v>46102</v>
       </c>
-      <c r="B27" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B27" s="76" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C27" s="68" t="n">
@@ -9518,9 +9534,9 @@
       <c r="A34" s="62" t="n">
         <v>46109</v>
       </c>
-      <c r="B34" s="76" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B34" s="77" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C34" s="72" t="n">
@@ -9586,7 +9602,7 @@
       <c r="A36" s="62" t="n">
         <v>46111</v>
       </c>
-      <c r="B36" s="76" t="inlineStr">
+      <c r="B36" s="78" t="inlineStr">
         <is>
           <t>P</t>
         </is>
@@ -9650,31 +9666,31 @@
           <t>إجمالي عدد الساعات :</t>
         </is>
       </c>
-      <c r="B38" s="77" t="n"/>
-      <c r="C38" s="78">
+      <c r="B38" s="79" t="n"/>
+      <c r="C38" s="80">
         <f>SUM(C7:C37) -  (COUNTIF(B7:B37, "AWO") * 8)</f>
         <v/>
       </c>
-      <c r="D38" s="79">
+      <c r="D38" s="81">
         <f>IFERROR(SUM(D7:D37), "")</f>
         <v/>
       </c>
-      <c r="E38" s="79">
+      <c r="E38" s="81">
         <f>IFERROR(SUM(E7:E37), "")</f>
         <v/>
       </c>
-      <c r="F38" s="79">
+      <c r="F38" s="81">
         <f>IFERROR(SUM(F7:F37), "")</f>
         <v/>
       </c>
       <c r="G38" s="13" t="n"/>
-      <c r="H38" s="80" t="n"/>
+      <c r="H38" s="82" t="n"/>
       <c r="I38" s="32" t="inlineStr">
         <is>
           <t>الملاحظات :</t>
         </is>
       </c>
-      <c r="J38" s="81" t="n"/>
+      <c r="J38" s="83" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1" s="44">
       <c r="A39" s="54" t="inlineStr">
@@ -9682,20 +9698,20 @@
           <t>إجمالي عدد ايام الدوام :</t>
         </is>
       </c>
-      <c r="B39" s="77" t="n"/>
-      <c r="C39" s="82">
+      <c r="B39" s="79" t="n"/>
+      <c r="C39" s="84">
         <f>COUNTIF(B7:B37, "P") + COUNTIF(B7:B37, "W") + COUNTIF(B7:B37, "H") + COUNTIF(B7:B37, "A") + COUNTIF(B7:B37, "AWO")-C40</f>
         <v/>
       </c>
-      <c r="D39" s="82" t="n"/>
-      <c r="E39" s="82" t="n"/>
-      <c r="F39" s="82" t="n"/>
+      <c r="D39" s="84" t="n"/>
+      <c r="E39" s="84" t="n"/>
+      <c r="F39" s="84" t="n"/>
       <c r="G39" s="35" t="inlineStr">
         <is>
           <t>الاجازات المرضية</t>
         </is>
       </c>
-      <c r="H39" s="83">
+      <c r="H39" s="85">
         <f>COUNTIF(B7:B37,"sl")</f>
         <v/>
       </c>
@@ -9703,7 +9719,7 @@
         <f>COUNTIFS(G7:G37, "SL", G7:G37, "&lt;=3")</f>
         <v/>
       </c>
-      <c r="J39" s="81" t="n"/>
+      <c r="J39" s="83" t="n"/>
     </row>
     <row r="40" ht="37.2" customHeight="1" s="44">
       <c r="A40" s="54" t="inlineStr">
@@ -9711,24 +9727,24 @@
           <t>إجمالي عدد ايام الغياب :</t>
         </is>
       </c>
-      <c r="B40" s="77" t="n"/>
-      <c r="C40" s="82">
+      <c r="B40" s="79" t="n"/>
+      <c r="C40" s="84">
         <f>COUNTIF(B7:B37,"A")+COUNTIF(B7:B37,"AWO")*2</f>
         <v/>
       </c>
-      <c r="D40" s="82" t="n"/>
-      <c r="E40" s="82" t="n"/>
-      <c r="F40" s="82" t="n"/>
+      <c r="D40" s="84" t="n"/>
+      <c r="E40" s="84" t="n"/>
+      <c r="F40" s="84" t="n"/>
       <c r="G40" s="33" t="inlineStr">
         <is>
           <t>قيمة الخصم الاضافي</t>
         </is>
       </c>
-      <c r="H40" s="84" t="n">
+      <c r="H40" s="86" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="47" t="n"/>
-      <c r="J40" s="81" t="n"/>
+      <c r="J40" s="83" t="n"/>
     </row>
     <row r="41" ht="37.2" customHeight="1" s="44">
       <c r="A41" s="54" t="inlineStr">
@@ -9736,25 +9752,25 @@
           <t>قيمة الخصم :</t>
         </is>
       </c>
-      <c r="B41" s="77" t="n"/>
-      <c r="C41" s="85">
+      <c r="B41" s="79" t="n"/>
+      <c r="C41" s="87">
         <f>COUNTIF(B7:B37,"AWO") * 2 * I3 +COUNTIF(B7:B37, "A") * I3</f>
         <v/>
       </c>
-      <c r="D41" s="82" t="n"/>
-      <c r="E41" s="82" t="n"/>
-      <c r="F41" s="86" t="n"/>
+      <c r="D41" s="84" t="n"/>
+      <c r="E41" s="84" t="n"/>
+      <c r="F41" s="88" t="n"/>
       <c r="G41" s="35" t="inlineStr">
         <is>
           <t>مجموع الخصم :</t>
         </is>
       </c>
-      <c r="H41" s="84">
+      <c r="H41" s="86">
         <f>SUM(C41+H40)</f>
         <v/>
       </c>
       <c r="I41" s="48" t="n"/>
-      <c r="J41" s="81" t="n"/>
+      <c r="J41" s="83" t="n"/>
     </row>
     <row r="42" ht="37.2" customHeight="1" s="44">
       <c r="A42" s="54" t="inlineStr">
@@ -9762,20 +9778,20 @@
           <t>إجمالي الأجر بعد الخصم :</t>
         </is>
       </c>
-      <c r="B42" s="77" t="n"/>
-      <c r="C42" s="87">
+      <c r="B42" s="79" t="n"/>
+      <c r="C42" s="89">
         <f>IF(F4&lt;&gt;"", I2/(DAY(EOMONTH(F2,0))*8)*C38, "")</f>
         <v/>
       </c>
-      <c r="D42" s="87">
+      <c r="D42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*1.25*D38, "")</f>
         <v/>
       </c>
-      <c r="E42" s="87">
+      <c r="E42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*1.5*E38, "")</f>
         <v/>
       </c>
-      <c r="F42" s="87">
+      <c r="F42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*2.5*F38, "")</f>
         <v/>
       </c>
@@ -9784,12 +9800,12 @@
           <t>: الإجمالي</t>
         </is>
       </c>
-      <c r="H42" s="77" t="n"/>
+      <c r="H42" s="79" t="n"/>
       <c r="I42" s="67">
         <f>IFERROR(SUM(C42:F42), "") - H40</f>
         <v/>
       </c>
-      <c r="J42" s="81" t="n"/>
+      <c r="J42" s="83" t="n"/>
     </row>
     <row r="43" ht="34.2" customHeight="1" s="44">
       <c r="A43" s="17" t="inlineStr">
@@ -9797,86 +9813,86 @@
           <t xml:space="preserve">التاريخ : </t>
         </is>
       </c>
-      <c r="B43" s="88">
+      <c r="B43" s="90">
         <f>TODAY()</f>
         <v/>
       </c>
-      <c r="C43" s="89" t="n"/>
-      <c r="D43" s="90" t="inlineStr">
+      <c r="C43" s="91" t="n"/>
+      <c r="D43" s="92" t="inlineStr">
         <is>
           <t xml:space="preserve">توقيع الموظف : </t>
         </is>
       </c>
-      <c r="E43" s="90" t="n"/>
-      <c r="F43" s="90" t="n"/>
+      <c r="E43" s="92" t="n"/>
+      <c r="F43" s="92" t="n"/>
       <c r="G43" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">توقيع المدير : </t>
         </is>
       </c>
-      <c r="H43" s="91" t="n"/>
+      <c r="H43" s="93" t="n"/>
       <c r="I43" s="18" t="n"/>
-      <c r="J43" s="81" t="n"/>
+      <c r="J43" s="83" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="19" t="n"/>
-      <c r="B44" s="92" t="n"/>
-      <c r="C44" s="92" t="n"/>
-      <c r="D44" s="92" t="n"/>
-      <c r="E44" s="92" t="n"/>
-      <c r="F44" s="92" t="n"/>
+      <c r="B44" s="94" t="n"/>
+      <c r="C44" s="94" t="n"/>
+      <c r="D44" s="94" t="n"/>
+      <c r="E44" s="94" t="n"/>
+      <c r="F44" s="94" t="n"/>
       <c r="G44" s="19" t="n"/>
-      <c r="H44" s="92" t="n"/>
+      <c r="H44" s="94" t="n"/>
       <c r="I44" s="19" t="n"/>
-      <c r="J44" s="81" t="n"/>
+      <c r="J44" s="83" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="19" t="n"/>
-      <c r="B45" s="92" t="n"/>
-      <c r="C45" s="92" t="n"/>
-      <c r="D45" s="92" t="n"/>
-      <c r="E45" s="92" t="n"/>
-      <c r="F45" s="92" t="n"/>
+      <c r="B45" s="94" t="n"/>
+      <c r="C45" s="94" t="n"/>
+      <c r="D45" s="94" t="n"/>
+      <c r="E45" s="94" t="n"/>
+      <c r="F45" s="94" t="n"/>
       <c r="G45" s="19" t="n"/>
-      <c r="H45" s="92" t="n"/>
+      <c r="H45" s="94" t="n"/>
       <c r="I45" s="19" t="n"/>
-      <c r="J45" s="81" t="n"/>
+      <c r="J45" s="83" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="81" t="n"/>
-      <c r="C46" s="81" t="n"/>
-      <c r="D46" s="81" t="n"/>
-      <c r="E46" s="81" t="n"/>
-      <c r="F46" s="81" t="n"/>
-      <c r="H46" s="81" t="n"/>
-      <c r="J46" s="81" t="n"/>
+      <c r="B46" s="83" t="n"/>
+      <c r="C46" s="83" t="n"/>
+      <c r="D46" s="83" t="n"/>
+      <c r="E46" s="83" t="n"/>
+      <c r="F46" s="83" t="n"/>
+      <c r="H46" s="83" t="n"/>
+      <c r="J46" s="83" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="81" t="n"/>
-      <c r="C47" s="81" t="n"/>
-      <c r="D47" s="81" t="n"/>
-      <c r="E47" s="81" t="n"/>
-      <c r="F47" s="81" t="n"/>
-      <c r="H47" s="81" t="n"/>
-      <c r="J47" s="81" t="n"/>
+      <c r="B47" s="83" t="n"/>
+      <c r="C47" s="83" t="n"/>
+      <c r="D47" s="83" t="n"/>
+      <c r="E47" s="83" t="n"/>
+      <c r="F47" s="83" t="n"/>
+      <c r="H47" s="83" t="n"/>
+      <c r="J47" s="83" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="81" t="n"/>
-      <c r="C48" s="81" t="n"/>
-      <c r="D48" s="81" t="n"/>
-      <c r="E48" s="81" t="n"/>
-      <c r="F48" s="81" t="n"/>
-      <c r="H48" s="81" t="n"/>
-      <c r="J48" s="81" t="n"/>
+      <c r="B48" s="83" t="n"/>
+      <c r="C48" s="83" t="n"/>
+      <c r="D48" s="83" t="n"/>
+      <c r="E48" s="83" t="n"/>
+      <c r="F48" s="83" t="n"/>
+      <c r="H48" s="83" t="n"/>
+      <c r="J48" s="83" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="81" t="n"/>
-      <c r="C49" s="81" t="n"/>
-      <c r="D49" s="81" t="n"/>
-      <c r="E49" s="81" t="n"/>
-      <c r="F49" s="81" t="n"/>
-      <c r="H49" s="81" t="n"/>
-      <c r="J49" s="81" t="n"/>
+      <c r="B49" s="83" t="n"/>
+      <c r="C49" s="83" t="n"/>
+      <c r="D49" s="83" t="n"/>
+      <c r="E49" s="83" t="n"/>
+      <c r="F49" s="83" t="n"/>
+      <c r="H49" s="83" t="n"/>
+      <c r="J49" s="83" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="45">
@@ -10302,9 +10318,9 @@
       <c r="A13" s="62" t="n">
         <v>46088</v>
       </c>
-      <c r="B13" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B13" s="76" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C13" s="68" t="n">
@@ -10544,9 +10560,9 @@
       <c r="A20" s="62" t="n">
         <v>46095</v>
       </c>
-      <c r="B20" s="71" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B20" s="76" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C20" s="72" t="n">
@@ -10701,7 +10717,7 @@
       </c>
       <c r="H24" s="75" t="inlineStr">
         <is>
-          <t>Al Karama Complex 4hrs + Home`s Mr.Abdullah 4hrs</t>
+          <t>Home`s Mr.Abdullah 4hrs + Al Karama Complex 4hrs</t>
         </is>
       </c>
       <c r="I24" s="34">
@@ -10790,9 +10806,9 @@
       <c r="A27" s="61" t="n">
         <v>46102</v>
       </c>
-      <c r="B27" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B27" s="76" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C27" s="68" t="n">
@@ -11032,9 +11048,9 @@
       <c r="A34" s="62" t="n">
         <v>46109</v>
       </c>
-      <c r="B34" s="76" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B34" s="77" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C34" s="72" t="n">
@@ -11102,7 +11118,7 @@
       <c r="A36" s="62" t="n">
         <v>46111</v>
       </c>
-      <c r="B36" s="76" t="inlineStr">
+      <c r="B36" s="78" t="inlineStr">
         <is>
           <t>P</t>
         </is>
@@ -11166,31 +11182,31 @@
           <t>إجمالي عدد الساعات :</t>
         </is>
       </c>
-      <c r="B38" s="77" t="n"/>
-      <c r="C38" s="78">
+      <c r="B38" s="79" t="n"/>
+      <c r="C38" s="80">
         <f>SUM(C7:C37) -  (COUNTIF(B7:B37, "AWO") * 8)</f>
         <v/>
       </c>
-      <c r="D38" s="79">
+      <c r="D38" s="81">
         <f>IFERROR(SUM(D7:D37), "")</f>
         <v/>
       </c>
-      <c r="E38" s="79">
+      <c r="E38" s="81">
         <f>IFERROR(SUM(E7:E37), "")</f>
         <v/>
       </c>
-      <c r="F38" s="79">
+      <c r="F38" s="81">
         <f>IFERROR(SUM(F7:F37), "")</f>
         <v/>
       </c>
       <c r="G38" s="13" t="n"/>
-      <c r="H38" s="80" t="n"/>
+      <c r="H38" s="82" t="n"/>
       <c r="I38" s="32" t="inlineStr">
         <is>
           <t>الملاحظات :</t>
         </is>
       </c>
-      <c r="J38" s="81" t="n"/>
+      <c r="J38" s="83" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1" s="44">
       <c r="A39" s="54" t="inlineStr">
@@ -11198,20 +11214,20 @@
           <t>إجمالي عدد ايام الدوام :</t>
         </is>
       </c>
-      <c r="B39" s="77" t="n"/>
-      <c r="C39" s="82">
+      <c r="B39" s="79" t="n"/>
+      <c r="C39" s="84">
         <f>COUNTIF(B7:B37, "P") + COUNTIF(B7:B37, "W") + COUNTIF(B7:B37, "H") + COUNTIF(B7:B37, "A") + COUNTIF(B7:B37, "AWO")-C40</f>
         <v/>
       </c>
-      <c r="D39" s="82" t="n"/>
-      <c r="E39" s="82" t="n"/>
-      <c r="F39" s="82" t="n"/>
+      <c r="D39" s="84" t="n"/>
+      <c r="E39" s="84" t="n"/>
+      <c r="F39" s="84" t="n"/>
       <c r="G39" s="35" t="inlineStr">
         <is>
           <t>الاجازات المرضية</t>
         </is>
       </c>
-      <c r="H39" s="83">
+      <c r="H39" s="85">
         <f>COUNTIF(B7:B37,"sl")</f>
         <v/>
       </c>
@@ -11219,7 +11235,7 @@
         <f>COUNTIFS(G7:G37, "SL", G7:G37, "&lt;=3")</f>
         <v/>
       </c>
-      <c r="J39" s="81" t="n"/>
+      <c r="J39" s="83" t="n"/>
     </row>
     <row r="40" ht="37.2" customHeight="1" s="44">
       <c r="A40" s="54" t="inlineStr">
@@ -11227,24 +11243,24 @@
           <t>إجمالي عدد ايام الغياب :</t>
         </is>
       </c>
-      <c r="B40" s="77" t="n"/>
-      <c r="C40" s="82">
+      <c r="B40" s="79" t="n"/>
+      <c r="C40" s="84">
         <f>COUNTIF(B7:B37,"A")+COUNTIF(B7:B37,"AWO")*2</f>
         <v/>
       </c>
-      <c r="D40" s="82" t="n"/>
-      <c r="E40" s="82" t="n"/>
-      <c r="F40" s="82" t="n"/>
+      <c r="D40" s="84" t="n"/>
+      <c r="E40" s="84" t="n"/>
+      <c r="F40" s="84" t="n"/>
       <c r="G40" s="33" t="inlineStr">
         <is>
           <t>قيمة الخصم الاضافي</t>
         </is>
       </c>
-      <c r="H40" s="84" t="n">
+      <c r="H40" s="86" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="47" t="n"/>
-      <c r="J40" s="81" t="n"/>
+      <c r="J40" s="83" t="n"/>
     </row>
     <row r="41" ht="37.2" customHeight="1" s="44">
       <c r="A41" s="54" t="inlineStr">
@@ -11252,25 +11268,25 @@
           <t>قيمة الخصم :</t>
         </is>
       </c>
-      <c r="B41" s="77" t="n"/>
-      <c r="C41" s="85">
+      <c r="B41" s="79" t="n"/>
+      <c r="C41" s="87">
         <f>COUNTIF(B7:B37,"AWO") * 2 * I3 +COUNTIF(B7:B37, "A") * I3</f>
         <v/>
       </c>
-      <c r="D41" s="82" t="n"/>
-      <c r="E41" s="82" t="n"/>
-      <c r="F41" s="86" t="n"/>
+      <c r="D41" s="84" t="n"/>
+      <c r="E41" s="84" t="n"/>
+      <c r="F41" s="88" t="n"/>
       <c r="G41" s="35" t="inlineStr">
         <is>
           <t>مجموع الخصم :</t>
         </is>
       </c>
-      <c r="H41" s="84">
+      <c r="H41" s="86">
         <f>SUM(C41+H40)</f>
         <v/>
       </c>
       <c r="I41" s="48" t="n"/>
-      <c r="J41" s="81" t="n"/>
+      <c r="J41" s="83" t="n"/>
     </row>
     <row r="42" ht="37.2" customHeight="1" s="44">
       <c r="A42" s="54" t="inlineStr">
@@ -11278,20 +11294,20 @@
           <t>إجمالي الأجر بعد الخصم :</t>
         </is>
       </c>
-      <c r="B42" s="77" t="n"/>
-      <c r="C42" s="87">
+      <c r="B42" s="79" t="n"/>
+      <c r="C42" s="89">
         <f>IF(F4&lt;&gt;"", I2/(DAY(EOMONTH(F2,0))*8)*C38, "")</f>
         <v/>
       </c>
-      <c r="D42" s="87">
+      <c r="D42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*1.25*D38, "")</f>
         <v/>
       </c>
-      <c r="E42" s="87">
+      <c r="E42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*1.5*E38, "")</f>
         <v/>
       </c>
-      <c r="F42" s="87">
+      <c r="F42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*2.5*F38, "")</f>
         <v/>
       </c>
@@ -11300,12 +11316,12 @@
           <t>: الإجمالي</t>
         </is>
       </c>
-      <c r="H42" s="77" t="n"/>
+      <c r="H42" s="79" t="n"/>
       <c r="I42" s="67">
         <f>IFERROR(SUM(C42:F42), "") - H40</f>
         <v/>
       </c>
-      <c r="J42" s="81" t="n"/>
+      <c r="J42" s="83" t="n"/>
     </row>
     <row r="43" ht="34.2" customHeight="1" s="44">
       <c r="A43" s="17" t="inlineStr">
@@ -11313,86 +11329,86 @@
           <t xml:space="preserve">التاريخ : </t>
         </is>
       </c>
-      <c r="B43" s="88">
+      <c r="B43" s="90">
         <f>TODAY()</f>
         <v/>
       </c>
-      <c r="C43" s="89" t="n"/>
-      <c r="D43" s="90" t="inlineStr">
+      <c r="C43" s="91" t="n"/>
+      <c r="D43" s="92" t="inlineStr">
         <is>
           <t xml:space="preserve">توقيع الموظف : </t>
         </is>
       </c>
-      <c r="E43" s="90" t="n"/>
-      <c r="F43" s="90" t="n"/>
+      <c r="E43" s="92" t="n"/>
+      <c r="F43" s="92" t="n"/>
       <c r="G43" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">توقيع المدير : </t>
         </is>
       </c>
-      <c r="H43" s="91" t="n"/>
+      <c r="H43" s="93" t="n"/>
       <c r="I43" s="18" t="n"/>
-      <c r="J43" s="81" t="n"/>
+      <c r="J43" s="83" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="19" t="n"/>
-      <c r="B44" s="92" t="n"/>
-      <c r="C44" s="92" t="n"/>
-      <c r="D44" s="92" t="n"/>
-      <c r="E44" s="92" t="n"/>
-      <c r="F44" s="92" t="n"/>
+      <c r="B44" s="94" t="n"/>
+      <c r="C44" s="94" t="n"/>
+      <c r="D44" s="94" t="n"/>
+      <c r="E44" s="94" t="n"/>
+      <c r="F44" s="94" t="n"/>
       <c r="G44" s="19" t="n"/>
-      <c r="H44" s="92" t="n"/>
+      <c r="H44" s="94" t="n"/>
       <c r="I44" s="19" t="n"/>
-      <c r="J44" s="81" t="n"/>
+      <c r="J44" s="83" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="19" t="n"/>
-      <c r="B45" s="92" t="n"/>
-      <c r="C45" s="92" t="n"/>
-      <c r="D45" s="92" t="n"/>
-      <c r="E45" s="92" t="n"/>
-      <c r="F45" s="92" t="n"/>
+      <c r="B45" s="94" t="n"/>
+      <c r="C45" s="94" t="n"/>
+      <c r="D45" s="94" t="n"/>
+      <c r="E45" s="94" t="n"/>
+      <c r="F45" s="94" t="n"/>
       <c r="G45" s="19" t="n"/>
-      <c r="H45" s="92" t="n"/>
+      <c r="H45" s="94" t="n"/>
       <c r="I45" s="19" t="n"/>
-      <c r="J45" s="81" t="n"/>
+      <c r="J45" s="83" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="81" t="n"/>
-      <c r="C46" s="81" t="n"/>
-      <c r="D46" s="81" t="n"/>
-      <c r="E46" s="81" t="n"/>
-      <c r="F46" s="81" t="n"/>
-      <c r="H46" s="81" t="n"/>
-      <c r="J46" s="81" t="n"/>
+      <c r="B46" s="83" t="n"/>
+      <c r="C46" s="83" t="n"/>
+      <c r="D46" s="83" t="n"/>
+      <c r="E46" s="83" t="n"/>
+      <c r="F46" s="83" t="n"/>
+      <c r="H46" s="83" t="n"/>
+      <c r="J46" s="83" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="81" t="n"/>
-      <c r="C47" s="81" t="n"/>
-      <c r="D47" s="81" t="n"/>
-      <c r="E47" s="81" t="n"/>
-      <c r="F47" s="81" t="n"/>
-      <c r="H47" s="81" t="n"/>
-      <c r="J47" s="81" t="n"/>
+      <c r="B47" s="83" t="n"/>
+      <c r="C47" s="83" t="n"/>
+      <c r="D47" s="83" t="n"/>
+      <c r="E47" s="83" t="n"/>
+      <c r="F47" s="83" t="n"/>
+      <c r="H47" s="83" t="n"/>
+      <c r="J47" s="83" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="81" t="n"/>
-      <c r="C48" s="81" t="n"/>
-      <c r="D48" s="81" t="n"/>
-      <c r="E48" s="81" t="n"/>
-      <c r="F48" s="81" t="n"/>
-      <c r="H48" s="81" t="n"/>
-      <c r="J48" s="81" t="n"/>
+      <c r="B48" s="83" t="n"/>
+      <c r="C48" s="83" t="n"/>
+      <c r="D48" s="83" t="n"/>
+      <c r="E48" s="83" t="n"/>
+      <c r="F48" s="83" t="n"/>
+      <c r="H48" s="83" t="n"/>
+      <c r="J48" s="83" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="81" t="n"/>
-      <c r="C49" s="81" t="n"/>
-      <c r="D49" s="81" t="n"/>
-      <c r="E49" s="81" t="n"/>
-      <c r="F49" s="81" t="n"/>
-      <c r="H49" s="81" t="n"/>
-      <c r="J49" s="81" t="n"/>
+      <c r="B49" s="83" t="n"/>
+      <c r="C49" s="83" t="n"/>
+      <c r="D49" s="83" t="n"/>
+      <c r="E49" s="83" t="n"/>
+      <c r="F49" s="83" t="n"/>
+      <c r="H49" s="83" t="n"/>
+      <c r="J49" s="83" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="45">
@@ -11814,9 +11830,9 @@
       <c r="A13" s="62" t="n">
         <v>46088</v>
       </c>
-      <c r="B13" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B13" s="76" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C13" s="68" t="n">
@@ -12052,9 +12068,9 @@
       <c r="A20" s="62" t="n">
         <v>46095</v>
       </c>
-      <c r="B20" s="71" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B20" s="76" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C20" s="72" t="n">
@@ -12290,9 +12306,9 @@
       <c r="A27" s="61" t="n">
         <v>46102</v>
       </c>
-      <c r="B27" s="68" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B27" s="76" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C27" s="68" t="n">
@@ -12528,9 +12544,9 @@
       <c r="A34" s="62" t="n">
         <v>46109</v>
       </c>
-      <c r="B34" s="76" t="inlineStr">
-        <is>
-          <t>P</t>
+      <c r="B34" s="77" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="C34" s="72" t="n">
@@ -12596,7 +12612,7 @@
       <c r="A36" s="62" t="n">
         <v>46111</v>
       </c>
-      <c r="B36" s="76" t="inlineStr">
+      <c r="B36" s="78" t="inlineStr">
         <is>
           <t>P</t>
         </is>
@@ -12660,31 +12676,31 @@
           <t>إجمالي عدد الساعات :</t>
         </is>
       </c>
-      <c r="B38" s="77" t="n"/>
-      <c r="C38" s="78">
+      <c r="B38" s="79" t="n"/>
+      <c r="C38" s="80">
         <f>SUM(C7:C37) -  (COUNTIF(B7:B37, "AWO") * 8)</f>
         <v/>
       </c>
-      <c r="D38" s="79">
+      <c r="D38" s="81">
         <f>IFERROR(SUM(D7:D37), "")</f>
         <v/>
       </c>
-      <c r="E38" s="79">
+      <c r="E38" s="81">
         <f>IFERROR(SUM(E7:E37), "")</f>
         <v/>
       </c>
-      <c r="F38" s="79">
+      <c r="F38" s="81">
         <f>IFERROR(SUM(F7:F37), "")</f>
         <v/>
       </c>
       <c r="G38" s="13" t="n"/>
-      <c r="H38" s="80" t="n"/>
+      <c r="H38" s="82" t="n"/>
       <c r="I38" s="32" t="inlineStr">
         <is>
           <t>الملاحظات :</t>
         </is>
       </c>
-      <c r="J38" s="81" t="n"/>
+      <c r="J38" s="83" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1" s="44">
       <c r="A39" s="54" t="inlineStr">
@@ -12692,20 +12708,20 @@
           <t>إجمالي عدد ايام الدوام :</t>
         </is>
       </c>
-      <c r="B39" s="77" t="n"/>
-      <c r="C39" s="82">
+      <c r="B39" s="79" t="n"/>
+      <c r="C39" s="84">
         <f>COUNTIF(B7:B37, "P") + COUNTIF(B7:B37, "W") + COUNTIF(B7:B37, "H") + COUNTIF(B7:B37, "A") + COUNTIF(B7:B37, "AWO")-C40</f>
         <v/>
       </c>
-      <c r="D39" s="82" t="n"/>
-      <c r="E39" s="82" t="n"/>
-      <c r="F39" s="82" t="n"/>
+      <c r="D39" s="84" t="n"/>
+      <c r="E39" s="84" t="n"/>
+      <c r="F39" s="84" t="n"/>
       <c r="G39" s="35" t="inlineStr">
         <is>
           <t>الاجازات المرضية</t>
         </is>
       </c>
-      <c r="H39" s="83">
+      <c r="H39" s="85">
         <f>COUNTIF(B7:B37,"sl")</f>
         <v/>
       </c>
@@ -12713,7 +12729,7 @@
         <f>COUNTIFS(G7:G37, "SL", G7:G37, "&lt;=3")</f>
         <v/>
       </c>
-      <c r="J39" s="81" t="n"/>
+      <c r="J39" s="83" t="n"/>
     </row>
     <row r="40" ht="37.2" customHeight="1" s="44">
       <c r="A40" s="54" t="inlineStr">
@@ -12721,24 +12737,24 @@
           <t>إجمالي عدد ايام الغياب :</t>
         </is>
       </c>
-      <c r="B40" s="77" t="n"/>
-      <c r="C40" s="82">
+      <c r="B40" s="79" t="n"/>
+      <c r="C40" s="84">
         <f>COUNTIF(B7:B37,"A")+COUNTIF(B7:B37,"AWO")*2</f>
         <v/>
       </c>
-      <c r="D40" s="82" t="n"/>
-      <c r="E40" s="82" t="n"/>
-      <c r="F40" s="82" t="n"/>
+      <c r="D40" s="84" t="n"/>
+      <c r="E40" s="84" t="n"/>
+      <c r="F40" s="84" t="n"/>
       <c r="G40" s="33" t="inlineStr">
         <is>
           <t>قيمة الخصم الاضافي</t>
         </is>
       </c>
-      <c r="H40" s="84" t="n">
+      <c r="H40" s="86" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="47" t="n"/>
-      <c r="J40" s="81" t="n"/>
+      <c r="J40" s="83" t="n"/>
     </row>
     <row r="41" ht="37.2" customHeight="1" s="44">
       <c r="A41" s="54" t="inlineStr">
@@ -12746,25 +12762,25 @@
           <t>قيمة الخصم :</t>
         </is>
       </c>
-      <c r="B41" s="77" t="n"/>
-      <c r="C41" s="85">
+      <c r="B41" s="79" t="n"/>
+      <c r="C41" s="87">
         <f>COUNTIF(B7:B37,"AWO") * 2 * I3 +COUNTIF(B7:B37, "A") * I3</f>
         <v/>
       </c>
-      <c r="D41" s="82" t="n"/>
-      <c r="E41" s="82" t="n"/>
-      <c r="F41" s="86" t="n"/>
+      <c r="D41" s="84" t="n"/>
+      <c r="E41" s="84" t="n"/>
+      <c r="F41" s="88" t="n"/>
       <c r="G41" s="35" t="inlineStr">
         <is>
           <t>مجموع الخصم :</t>
         </is>
       </c>
-      <c r="H41" s="84">
+      <c r="H41" s="86">
         <f>SUM(C41+H40)</f>
         <v/>
       </c>
       <c r="I41" s="48" t="n"/>
-      <c r="J41" s="81" t="n"/>
+      <c r="J41" s="83" t="n"/>
     </row>
     <row r="42" ht="37.2" customHeight="1" s="44">
       <c r="A42" s="54" t="inlineStr">
@@ -12772,20 +12788,20 @@
           <t>إجمالي الأجر بعد الخصم :</t>
         </is>
       </c>
-      <c r="B42" s="77" t="n"/>
-      <c r="C42" s="87">
+      <c r="B42" s="79" t="n"/>
+      <c r="C42" s="89">
         <f>IF(F4&lt;&gt;"", I2/(DAY(EOMONTH(F2,0))*8)*C38, "")</f>
         <v/>
       </c>
-      <c r="D42" s="87">
+      <c r="D42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*1.25*D38, "")</f>
         <v/>
       </c>
-      <c r="E42" s="87">
+      <c r="E42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*1.5*E38, "")</f>
         <v/>
       </c>
-      <c r="F42" s="87">
+      <c r="F42" s="89">
         <f>IFERROR(I2/(DAY(EOMONTH(F2,0))*8)*2.5*F38, "")</f>
         <v/>
       </c>
@@ -12794,12 +12810,12 @@
           <t>: الإجمالي</t>
         </is>
       </c>
-      <c r="H42" s="77" t="n"/>
+      <c r="H42" s="79" t="n"/>
       <c r="I42" s="67">
         <f>IFERROR(SUM(C42:F42), "") - H40</f>
         <v/>
       </c>
-      <c r="J42" s="81" t="n"/>
+      <c r="J42" s="83" t="n"/>
     </row>
     <row r="43" ht="34.2" customHeight="1" s="44">
       <c r="A43" s="17" t="inlineStr">
@@ -12807,86 +12823,86 @@
           <t xml:space="preserve">التاريخ : </t>
         </is>
       </c>
-      <c r="B43" s="88">
+      <c r="B43" s="90">
         <f>TODAY()</f>
         <v/>
       </c>
-      <c r="C43" s="89" t="n"/>
-      <c r="D43" s="90" t="inlineStr">
+      <c r="C43" s="91" t="n"/>
+      <c r="D43" s="92" t="inlineStr">
         <is>
           <t xml:space="preserve">توقيع الموظف : </t>
         </is>
       </c>
-      <c r="E43" s="90" t="n"/>
-      <c r="F43" s="90" t="n"/>
+      <c r="E43" s="92" t="n"/>
+      <c r="F43" s="92" t="n"/>
       <c r="G43" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">توقيع المدير : </t>
         </is>
       </c>
-      <c r="H43" s="91" t="n"/>
+      <c r="H43" s="93" t="n"/>
       <c r="I43" s="18" t="n"/>
-      <c r="J43" s="81" t="n"/>
+      <c r="J43" s="83" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="19" t="n"/>
-      <c r="B44" s="92" t="n"/>
-      <c r="C44" s="92" t="n"/>
-      <c r="D44" s="92" t="n"/>
-      <c r="E44" s="92" t="n"/>
-      <c r="F44" s="92" t="n"/>
+      <c r="B44" s="94" t="n"/>
+      <c r="C44" s="94" t="n"/>
+      <c r="D44" s="94" t="n"/>
+      <c r="E44" s="94" t="n"/>
+      <c r="F44" s="94" t="n"/>
       <c r="G44" s="19" t="n"/>
-      <c r="H44" s="92" t="n"/>
+      <c r="H44" s="94" t="n"/>
       <c r="I44" s="19" t="n"/>
-      <c r="J44" s="81" t="n"/>
+      <c r="J44" s="83" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="19" t="n"/>
-      <c r="B45" s="92" t="n"/>
-      <c r="C45" s="92" t="n"/>
-      <c r="D45" s="92" t="n"/>
-      <c r="E45" s="92" t="n"/>
-      <c r="F45" s="92" t="n"/>
+      <c r="B45" s="94" t="n"/>
+      <c r="C45" s="94" t="n"/>
+      <c r="D45" s="94" t="n"/>
+      <c r="E45" s="94" t="n"/>
+      <c r="F45" s="94" t="n"/>
       <c r="G45" s="19" t="n"/>
-      <c r="H45" s="92" t="n"/>
+      <c r="H45" s="94" t="n"/>
       <c r="I45" s="19" t="n"/>
-      <c r="J45" s="81" t="n"/>
+      <c r="J45" s="83" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="81" t="n"/>
-      <c r="C46" s="81" t="n"/>
-      <c r="D46" s="81" t="n"/>
-      <c r="E46" s="81" t="n"/>
-      <c r="F46" s="81" t="n"/>
-      <c r="H46" s="81" t="n"/>
-      <c r="J46" s="81" t="n"/>
+      <c r="B46" s="83" t="n"/>
+      <c r="C46" s="83" t="n"/>
+      <c r="D46" s="83" t="n"/>
+      <c r="E46" s="83" t="n"/>
+      <c r="F46" s="83" t="n"/>
+      <c r="H46" s="83" t="n"/>
+      <c r="J46" s="83" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="81" t="n"/>
-      <c r="C47" s="81" t="n"/>
-      <c r="D47" s="81" t="n"/>
-      <c r="E47" s="81" t="n"/>
-      <c r="F47" s="81" t="n"/>
-      <c r="H47" s="81" t="n"/>
-      <c r="J47" s="81" t="n"/>
+      <c r="B47" s="83" t="n"/>
+      <c r="C47" s="83" t="n"/>
+      <c r="D47" s="83" t="n"/>
+      <c r="E47" s="83" t="n"/>
+      <c r="F47" s="83" t="n"/>
+      <c r="H47" s="83" t="n"/>
+      <c r="J47" s="83" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="81" t="n"/>
-      <c r="C48" s="81" t="n"/>
-      <c r="D48" s="81" t="n"/>
-      <c r="E48" s="81" t="n"/>
-      <c r="F48" s="81" t="n"/>
-      <c r="H48" s="81" t="n"/>
-      <c r="J48" s="81" t="n"/>
+      <c r="B48" s="83" t="n"/>
+      <c r="C48" s="83" t="n"/>
+      <c r="D48" s="83" t="n"/>
+      <c r="E48" s="83" t="n"/>
+      <c r="F48" s="83" t="n"/>
+      <c r="H48" s="83" t="n"/>
+      <c r="J48" s="83" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="81" t="n"/>
-      <c r="C49" s="81" t="n"/>
-      <c r="D49" s="81" t="n"/>
-      <c r="E49" s="81" t="n"/>
-      <c r="F49" s="81" t="n"/>
-      <c r="H49" s="81" t="n"/>
-      <c r="J49" s="81" t="n"/>
+      <c r="B49" s="83" t="n"/>
+      <c r="C49" s="83" t="n"/>
+      <c r="D49" s="83" t="n"/>
+      <c r="E49" s="83" t="n"/>
+      <c r="F49" s="83" t="n"/>
+      <c r="H49" s="83" t="n"/>
+      <c r="J49" s="83" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="45">
